--- a/Product_Source/移动剪叉式升降平台园林高空作业维修车全自动液压自行走升降机/移动剪叉式升降平台园林高空作业维修车全自动液压自行走升降机.xlsx
+++ b/Product_Source/移动剪叉式升降平台园林高空作业维修车全自动液压自行走升降机/移动剪叉式升降平台园林高空作业维修车全自动液压自行走升降机.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AA_Project\Enterprise_Web\hntzs\Data\1688\移动剪叉式升降平台园林高空作业维修车全自动液压自行走升降机\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\AA_Project\Enterprise_Web\hntzs\technological-trappist\Product_Source\移动剪叉式升降平台园林高空作业维修车全自动液压自行走升降机\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E15FB7-AECD-4C2D-9C12-DBF57BE9B38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC47E21-F7BF-4D7A-9A29-B89D27F5F77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="62">
   <si>
     <t>产品规格</t>
   </si>
@@ -70,9 +70,6 @@
   </si>
   <si>
     <t>价格 | 库存(台)</t>
-  </si>
-  <si>
-    <t>进货数量</t>
   </si>
   <si>
     <t>产品信息电子图册</t>
@@ -542,7 +539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.625" bestFit="1" customWidth="1"/>
@@ -558,7 +555,7 @@
     <col min="15" max="15" width="13.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -604,381 +601,378 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>19</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>20</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>21</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>24</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>26</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>27</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>28</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
       </c>
       <c r="O2" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>32</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>33</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>34</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>35</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>36</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>37</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>38</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>39</v>
       </c>
-      <c r="K3" t="s">
-        <v>40</v>
-      </c>
       <c r="L3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M3">
         <v>3000</v>
       </c>
       <c r="N3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O3" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" t="s">
         <v>41</v>
       </c>
-      <c r="B4" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" t="s">
         <v>42</v>
       </c>
-      <c r="D4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>43</v>
       </c>
-      <c r="F4" t="s">
-        <v>44</v>
-      </c>
       <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
         <v>36</v>
-      </c>
-      <c r="H4" t="s">
-        <v>37</v>
       </c>
       <c r="I4">
         <v>0.78</v>
       </c>
       <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
         <v>39</v>
       </c>
-      <c r="K4" t="s">
-        <v>40</v>
-      </c>
       <c r="L4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M4">
         <v>3000</v>
       </c>
       <c r="N4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O4" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" t="s">
         <v>45</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
         <v>46</v>
       </c>
-      <c r="C5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>47</v>
       </c>
-      <c r="F5" t="s">
-        <v>48</v>
-      </c>
       <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
         <v>36</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
       </c>
       <c r="I5">
         <v>1.1599999999999999</v>
       </c>
       <c r="J5" t="s">
+        <v>38</v>
+      </c>
+      <c r="K5" t="s">
         <v>39</v>
       </c>
-      <c r="K5" t="s">
-        <v>40</v>
-      </c>
       <c r="L5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M5">
         <v>3000</v>
       </c>
       <c r="N5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O5" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" t="s">
         <v>49</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s">
         <v>46</v>
       </c>
-      <c r="C6" t="s">
+      <c r="F6" t="s">
         <v>50</v>
       </c>
-      <c r="D6" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
-      </c>
       <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
         <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
       </c>
       <c r="I6">
         <v>1.1599999999999999</v>
       </c>
       <c r="J6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" t="s">
         <v>39</v>
       </c>
-      <c r="K6" t="s">
-        <v>40</v>
-      </c>
       <c r="L6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M6">
         <v>3000</v>
       </c>
       <c r="N6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O6" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" t="s">
         <v>52</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>53</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
         <v>54</v>
       </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
       <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
         <v>36</v>
-      </c>
-      <c r="H7" t="s">
-        <v>37</v>
       </c>
       <c r="I7">
         <v>1.1599999999999999</v>
       </c>
       <c r="J7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K7" t="s">
         <v>39</v>
       </c>
-      <c r="K7" t="s">
-        <v>40</v>
-      </c>
       <c r="L7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M7">
         <v>3000</v>
       </c>
       <c r="N7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O7" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
         <v>56</v>
       </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
         <v>57</v>
       </c>
-      <c r="D8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
       <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
         <v>36</v>
-      </c>
-      <c r="H8" t="s">
-        <v>37</v>
       </c>
       <c r="I8">
         <v>1.1599999999999999</v>
       </c>
       <c r="J8" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" t="s">
         <v>39</v>
       </c>
-      <c r="K8" t="s">
-        <v>40</v>
-      </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M8">
         <v>3000</v>
       </c>
       <c r="N8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O8" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B9" t="s">
         <v>59</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>60</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
         <v>61</v>
       </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" t="s">
-        <v>62</v>
-      </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
         <v>36</v>
-      </c>
-      <c r="H9" t="s">
-        <v>37</v>
       </c>
       <c r="I9">
         <v>1.23</v>
       </c>
       <c r="J9" t="s">
+        <v>38</v>
+      </c>
+      <c r="K9" t="s">
         <v>39</v>
       </c>
-      <c r="K9" t="s">
-        <v>40</v>
-      </c>
       <c r="L9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M9">
         <v>3000</v>
       </c>
       <c r="N9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O9" s="1">
         <v>1000</v>
